--- a/Sajjad data/by_country_and_state/USA/KS.xlsx
+++ b/Sajjad data/by_country_and_state/USA/KS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="230">
   <si>
     <t>Business Name</t>
   </si>
@@ -164,6 +164,543 @@
   </si>
   <si>
     <t>2026-10-25T09:21:21.827Z</t>
+  </si>
+  <si>
+    <t>Kimberly Nguyen Family Dentistry</t>
+  </si>
+  <si>
+    <t>(316) 612-7777</t>
+  </si>
+  <si>
+    <t>7520 E Harry St, Wichita, KS 67207</t>
+  </si>
+  <si>
+    <t>Wichita</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>SundayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Kimberly+Nguyen+Family+Dentistry/data=!4m7!3m6!1s0x87bafb5bcf68319f:0xc8fc05e0ec9e955d!8m2!3d37.6651428!4d-97.2488897!16s%2Fg%2F1q2whs085!19sChIJnzFoz1v7uocRXZWe7OAF_Mg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:13:48.934Z</t>
+  </si>
+  <si>
+    <t>Dr. Harrison Black</t>
+  </si>
+  <si>
+    <t>(316) 223-4455</t>
+  </si>
+  <si>
+    <t>Pediatric dentist</t>
+  </si>
+  <si>
+    <t>3305 E Douglas Ave Ste 101, Wichita, KS 67218</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Harrison+Black/data=!4m7!3m6!1s0x87bae36d98f52aff:0x2f2903ee34ac8f31!8m2!3d37.6861342!4d-97.2963973!16s%2Fg%2F11qgb79zc8!19sChIJ_yr1mG3juocRMY-sNO4DKS8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:14:25.458Z</t>
+  </si>
+  <si>
+    <t>Dr. Rebecca Parr (Pediatric Dentist)</t>
+  </si>
+  <si>
+    <t>(316) 613-2077</t>
+  </si>
+  <si>
+    <t>6943 W 37th St N, Wichita, KS 67205</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Rebecca+Parr+%28Pediatric+Dentist%29/data=!4m7!3m6!1s0x87bb1fe440855555:0x94e54211e1509c0e!8m2!3d37.7515999!4d-97.4233062!16s%2Fg%2F11rwxfwp7x!19sChIJVVWFQOQfu4cRDpxQ4RFC5ZQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:14:27.255Z</t>
+  </si>
+  <si>
+    <t>Anderson Orthodontics Laboratory</t>
+  </si>
+  <si>
+    <t>(316) 942-8703</t>
+  </si>
+  <si>
+    <t>Laboratory</t>
+  </si>
+  <si>
+    <t>4318 W Central Ave, Wichita, KS 67212</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Anderson+Orthodontics+Laboratory/data=!4m7!3m6!1s0x87bae102eb240b55:0x784156993669291d!8m2!3d37.6950227!4d-97.393493!16s%2Fg%2F11bt_h_wbp!19sChIJVQsk6wLhuocRHSlpNplWQXg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:14:43.356Z</t>
+  </si>
+  <si>
+    <t>After Hours Dental Service</t>
+  </si>
+  <si>
+    <t>(316) 778-6761</t>
+  </si>
+  <si>
+    <t>935 S Glendale Ave, Wichita, KS 67218</t>
+  </si>
+  <si>
+    <t>3.7</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/After+Hours+Dental+Service/data=!4m7!3m6!1s0x87bae38ff04f0d99:0xb64fe24270c35ae!8m2!3d37.6707141!4d-97.2793744!16s%2Fg%2F11vhs9vf9z!19sChIJmQ1P8I_juocRrjUMJyT-ZAs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:15:29.607Z</t>
+  </si>
+  <si>
+    <t>Dental 911</t>
+  </si>
+  <si>
+    <t>(316) 262-1911</t>
+  </si>
+  <si>
+    <t>2610 S Seneca St #104, Wichita, KS 67217</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+911/data=!4m7!3m6!1s0x87bae6a09b7126f7:0xe8d41193b606f94b!8m2!3d37.6471061!4d-97.3522033!16s%2Fg%2F1tl7p70d!19sChIJ9yZxm6DmuocRS_kGtpMR1Og?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:15:33.124Z</t>
+  </si>
+  <si>
+    <t>Emergency Dental Guide</t>
+  </si>
+  <si>
+    <t>(316) 745-4025</t>
+  </si>
+  <si>
+    <t>6100 E 21st St N Suite 120, Wichita, KS 67208</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emergency+Dental+Guide/data=!4m7!3m6!1s0x87bae3b3235bc637:0x8ca0699f624d83dd!8m2!3d37.7233502!4d-97.2654918!16s%2Fg%2F11p1rfsd_n!19sChIJN8ZbI7PjuocR3YNNYp9poIw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:15:36.758Z</t>
+  </si>
+  <si>
+    <t>Carter Pediatric Dentistry and Orthodontics</t>
+  </si>
+  <si>
+    <t>(913) 451-1443</t>
+  </si>
+  <si>
+    <t>8005 W 110th St, Overland Park, KS 66210</t>
+  </si>
+  <si>
+    <t>4.4</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Carter+Pediatric+Dentistry+and+Orthodontics/data=!4m7!3m6!1s0x87c0ea5117cc4d97:0x1537558d5200d3a3!8m2!3d38.9286071!4d-94.6798731!16s%2Fg%2F1tdl6n7x!19sChIJl03MF1HqwIcRo9MAUo1VNxU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:18:51.643Z</t>
+  </si>
+  <si>
+    <t>Periodontist, P.A.</t>
+  </si>
+  <si>
+    <t>(913) 451-6158</t>
+  </si>
+  <si>
+    <t>10870 Benson St #21 #2100, Overland Park, KS 66210</t>
+  </si>
+  <si>
+    <t>462</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Periodontist,+P.A./data=!4m7!3m6!1s0x87c0eaff3d9df023:0xd0a71938d0939de5!8m2!3d38.9313107!4d-94.6888825!16s%2Fg%2F1tf_1lrs!19sChIJI_CdPf_qwIcR5Z2T0DgZp9A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:20:24.449Z</t>
+  </si>
+  <si>
+    <t>Hines &amp; Tull Periodontics</t>
+  </si>
+  <si>
+    <t>(913) 491-5548</t>
+  </si>
+  <si>
+    <t>4601 W 109th St, Overland Park, KS 66211</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hines+%26+Tull+Periodontics/data=!4m7!3m6!1s0x87c0ec00a2e9e151:0xc48b48c244f08b0f!8m2!3d38.9300563!4d-94.6389268!16s%2Fg%2F1thxr4r3!19sChIJUeHpogDswIcRD4vwRMJIi8Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:20:26.752Z</t>
+  </si>
+  <si>
+    <t>Foundation Periodontics</t>
+  </si>
+  <si>
+    <t>(913) 894-9962</t>
+  </si>
+  <si>
+    <t>8704 Bourgade St #100, Lenexa, KS 66219</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>SundayClosed; Monday8 AM–4 PM; Tuesday8 AM–4 PM; Wednesday8 AM–4 PM; Thursday8 AM–4 PM; FridayClosed; SaturdayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Foundation+Periodontics/data=!4m7!3m6!1s0x87c09480ee856a77:0x13148c588d538bcf!8m2!3d38.9706192!4d-94.7680282!16s%2Fg%2F1tj89yx5!19sChIJd2qF7oCUwIcRz4tTjViMFBM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:20:28.656Z</t>
+  </si>
+  <si>
+    <t>Hhd Periodontics: Bruner Jr Hugh H DDS</t>
+  </si>
+  <si>
+    <t>(913) 469-1612</t>
+  </si>
+  <si>
+    <t>4860 College Blvd Ste 114, Overland Park, KS 66211</t>
+  </si>
+  <si>
+    <t>513</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hhd+Periodontics:+Bruner+Jr+Hugh+H+DDS/data=!4m7!3m6!1s0x87c0e9863604b531:0x3f22979802b7217a!8m2!3d38.9284009!4d-94.6420921!16s%2Fg%2F1vknpxk5!19sChIJMbUENobpwIcReiG3ApiXIj8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:20:30.447Z</t>
+  </si>
+  <si>
+    <t>Dr. Joe M. Herrera, DDS</t>
+  </si>
+  <si>
+    <t>(913) 362-8868</t>
+  </si>
+  <si>
+    <t>701 Washington Blvd, Kansas City, KS 66101</t>
+  </si>
+  <si>
+    <t>Sunday9 AM–2 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Joe+M.+Herrera,+DDS/data=!4m7!3m6!1s0x87c0f16c59712d7d:0x4c6971f5d8edcf55!8m2!3d39.1176693!4d-94.6275819!16s%2Fg%2F1xg5t5yg!19sChIJfS1xWWzxwIcRVc_t2PVxaUw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:20:46.528Z</t>
+  </si>
+  <si>
+    <t>Dental Implants Kansas City</t>
+  </si>
+  <si>
+    <t>(913) 491-6282</t>
+  </si>
+  <si>
+    <t>11100 Ash St Suite #204, Leawood, KS 66211</t>
+  </si>
+  <si>
+    <t>Leawood</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Implants+Kansas+City/data=!4m7!3m6!1s0x87c0ea27d59aa3c1:0x578cea6172ddfea9!8m2!3d38.9266531!4d-94.6474178!16s%2Fg%2F11fl9h2h6y!19sChIJwaOa1SfqwIcRqf7dcmHqjFc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:22:11.661Z</t>
+  </si>
+  <si>
+    <t>Dr. Carol J. Jones, DDS</t>
+  </si>
+  <si>
+    <t>(913) 321-4385</t>
+  </si>
+  <si>
+    <t>707 Minnesota Ave, Kansas City, KS 66101</t>
+  </si>
+  <si>
+    <t>3.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Carol+J.+Jones,+DDS/data=!4m7!3m6!1s0x87c0f16da4dd2cc5:0x7c0f4891714bf6d9!8m2!3d39.1152682!4d-94.6271297!16s%2Fg%2F1thffzdw!19sChIJxSzdpG3xwIcR2fZLcZFID3w?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:22:53.133Z</t>
+  </si>
+  <si>
+    <t>Dr. Tyson E. Marrs, DDS</t>
+  </si>
+  <si>
+    <t>(913) 381-5194</t>
+  </si>
+  <si>
+    <t>3700 W 83rd St #103, Prairie Village, KS 66208</t>
+  </si>
+  <si>
+    <t>Prairie Village</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Tyson+E.+Marrs,+DDS/data=!4m7!3m6!1s0x87c0e94b4806b709:0x4bbf101983d9b22b!8m2!3d38.9789727!4d-94.6282063!16s%2Fg%2F1tg68ms7!19sChIJCbcGSEvpwIcRK7LZgxkQv0s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:23:17.899Z</t>
+  </si>
+  <si>
+    <t>South Topeka Dental Care</t>
+  </si>
+  <si>
+    <t>(785) 266-3533</t>
+  </si>
+  <si>
+    <t>1401 SW 37th St A, Topeka, KS 66611</t>
+  </si>
+  <si>
+    <t>Topeka</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/South+Topeka+Dental+Care/data=!4m7!3m6!1s0x87bf1d24719966f1:0xf108e3f0b23f207f!8m2!3d39.0002908!4d-95.696155!16s%2Fg%2F1td0h0bg!19sChIJ8WaZcSQdv4cRfyA_svDjCPE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:23:30.385Z</t>
+  </si>
+  <si>
+    <t>Dr. Carrie B. Peterson, DDS</t>
+  </si>
+  <si>
+    <t>(785) 266-9100</t>
+  </si>
+  <si>
+    <t>3316 SE 28th Terrace, Topeka, KS 66605</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Carrie+B.+Peterson,+DDS/data=!4m7!3m6!1s0x87bf1cb2620269f7:0xa6d65da9239e1da5!8m2!3d39.0164792!4d-95.6200339!16s%2Fg%2F1tdhfj44!19sChIJ92kCYrIcv4cRpR2eI6ld1qY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:23:34.856Z</t>
+  </si>
+  <si>
+    <t>Dr. Anthony T. Beckler, DDS</t>
+  </si>
+  <si>
+    <t>(785) 267-6886</t>
+  </si>
+  <si>
+    <t>2400 SW 29th St #224, Topeka, KS 66611</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Anthony+T.+Beckler,+DDS/data=!4m7!3m6!1s0x87bf02cab1ce46c7:0x35d5b477d394d11f!8m2!3d39.0155071!4d-95.7083073!16s%2Fg%2F1tq4rltw!19sChIJx0bOscoCv4cRH9GU03e01TU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:23:37.019Z</t>
+  </si>
+  <si>
+    <t>Lorie M. Baumgardner, DDS</t>
+  </si>
+  <si>
+    <t>(785) 272-0333</t>
+  </si>
+  <si>
+    <t>1125 SW Gage Blvd Ste a, Topeka, KS 66604</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lorie+M.+Baumgardner,+DDS/data=!4m7!3m6!1s0x87bf029d61c6fee9:0x49e0c79521371f4f!8m2!3d39.0485992!4d-95.7263412!16s%2Fg%2F1tlwg4sd!19sChIJ6f7GYZ0Cv4cRTx83IZXH4Ek?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:23:50.690Z</t>
+  </si>
+  <si>
+    <t>Jeffrey B. Clark, DDS</t>
+  </si>
+  <si>
+    <t>(785) 273-2565</t>
+  </si>
+  <si>
+    <t>5990 SW 28th St D, Topeka, KS 66614</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jeffrey+B.+Clark,+DDS/data=!4m7!3m6!1s0x87befd2df5651e1b:0x22895d538b24bd8b!8m2!3d39.016374!4d-95.761614!16s%2Fg%2F1tf3pd_q!19sChIJGx5l9S39vocRi70ki1NdiSI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:23:52.664Z</t>
+  </si>
+  <si>
+    <t>Dr. Robert A. Exon, DDS</t>
+  </si>
+  <si>
+    <t>(785) 232-7707</t>
+  </si>
+  <si>
+    <t>1919 SW 10th Ave #102, Topeka, KS 66604</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Robert+A.+Exon,+DDS/data=!4m7!3m6!1s0x87bf02f12876b26d:0xcbf440edd9707611!8m2!3d39.0510759!4d-95.7011693!16s%2Fg%2F1tdwl0bk!19sChIJbbJ2KPECv4cREXZw2e1A9Ms?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:23:54.861Z</t>
+  </si>
+  <si>
+    <t>Dr. Shabnam Amin, DDS</t>
+  </si>
+  <si>
+    <t>(785) 267-9500</t>
+  </si>
+  <si>
+    <t>2037 SE 29th St, Topeka, KS 66605</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Shabnam+Amin,+DDS/data=!4m7!3m6!1s0x87bf1cabaaea412b:0x5294795219adac65!8m2!3d39.0136984!4d-95.6494922!16s%2Fg%2F1tgnb3sd!19sChIJK0Hqqqscv4cRZaytGVJ5lFI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:23:56.700Z</t>
+  </si>
+  <si>
+    <t>Dr. Eric C. Johnson, DDS</t>
+  </si>
+  <si>
+    <t>(785) 273-4770</t>
+  </si>
+  <si>
+    <t>5601 SW Barrington Ct S Ste 1, Topeka, KS 66614</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Eric+C.+Johnson,+DDS/data=!4m7!3m6!1s0x87bf029d725dfca5:0xe6371f4b6cbcba1c!8m2!3d39.0165328!4d-95.7501055!16s%2Fg%2F1tfb2j1l!19sChIJpfxdcp0Cv4cRHLq8bEsfN-Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:23:58.901Z</t>
+  </si>
+  <si>
+    <t>Dean A. Troyer DDS</t>
+  </si>
+  <si>
+    <t>(785) 273-4410</t>
+  </si>
+  <si>
+    <t>Endodontist</t>
+  </si>
+  <si>
+    <t>2445 SW Wanamaker Rd, Topeka, KS 66614</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dean+A.+Troyer+DDS/data=!4m7!3m6!1s0x87bf029d61c6fee9:0x2819778ff63c9fca!8m2!3d39.0216734!4d-95.7629413!16s%2Fg%2F1tdgvxs6!19sChIJ6f7GYZ0Cv4cRyp889o93GSg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:24:00.966Z</t>
+  </si>
+  <si>
+    <t>Drs Hamilton &amp; Wilson</t>
+  </si>
+  <si>
+    <t>(785) 272-3722</t>
+  </si>
+  <si>
+    <t>Orthodontist</t>
+  </si>
+  <si>
+    <t>2235 SW Westport Dr, Topeka, KS 66614</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Drs+Hamilton+%26+Wilson/data=!4m7!3m6!1s0x87befb2c00000001:0x3748b9c53574a528!8m2!3d39.0259371!4d-95.757269!16s%2Fg%2F1tdc14lc!19sChIJAQAAACz7vocRKKV0NcW5SDc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:24:02.823Z</t>
+  </si>
+  <si>
+    <t>Jason Weber</t>
+  </si>
+  <si>
+    <t>(785) 273-2922</t>
+  </si>
+  <si>
+    <t>2930 SW Wanamaker Dr DR7, Topeka, KS 66614</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jason+Weber/data=!4m7!3m6!1s0x87befd3346cfffff:0xe8dd963afada9d5a!8m2!3d39.0135012!4d-95.7574262!16s%2Fg%2F11sc_y8j11!19sChIJ___PRjP9vocRWp3a-jqW3eg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:24:25.693Z</t>
+  </si>
+  <si>
+    <t>The Kids Dentist</t>
+  </si>
+  <si>
+    <t>(785) 266-2208</t>
+  </si>
+  <si>
+    <t>1230 SW Harvey St, Topeka, KS 66604</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/The+Kids+Dentist/data=!4m7!3m6!1s0x87befd0ded0fffff:0x828fb91977757f6!8m2!3d39.0446398!4d-95.7551652!16s%2Fg%2F11t9_t871x!19sChIJ__8P7Q39vocR9ld3l5H7KAg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:24:34.288Z</t>
+  </si>
+  <si>
+    <t>Dental Connect Group</t>
+  </si>
+  <si>
+    <t>(785) 601-0129</t>
+  </si>
+  <si>
+    <t>2853 S Kansas Ave, Topeka, KS 66611</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Connect+Group/data=!4m7!3m6!1s0x87bf03428bba0881:0x9b65e57a2334f4dd!8m2!3d39.01658!4d-95.68229!16s%2Fg%2F11zxj7jptc!19sChIJgQi6i0IDv4cR3fQ0I3rlZZs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:25:10.086Z</t>
+  </si>
+  <si>
+    <t>Stefania Caracioni DDS</t>
+  </si>
+  <si>
+    <t>(785) 246-6300</t>
+  </si>
+  <si>
+    <t>5100 SW 28th St, Topeka, KS 66614</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Stefania+Caracioni+DDS/data=!4m7!3m6!1s0x87befd32d58133fd:0xa19fe5fed723247c!8m2!3d39.016646!4d-95.7416486!16s%2Fg%2F1v9gv_3g!19sChIJ_TOB1TL9vocRfCQj1_7ln6E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:25:32.395Z</t>
+  </si>
+  <si>
+    <t>Humana in Topeka</t>
+  </si>
+  <si>
+    <t>(737) 248-7823</t>
+  </si>
+  <si>
+    <t>Corporate office</t>
+  </si>
+  <si>
+    <t>5310 SW 37th St, Topeka, KS 66614</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Humana+in+Topeka/data=!4m7!3m6!1s0x87bee2b9a2af5021:0x79be77978f8cd8eb!8m2!3d39.0008196!4d-95.7470828!16s%2Fg%2F1th0nd_l!19sChIJIVCvornivocR69iMj5d3vnk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:25:34.273Z</t>
   </si>
 </sst>
 </file>
@@ -544,7 +1081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -766,6 +1303,1277 @@
         <v>50</v>
       </c>
     </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" t="s">
+        <v>57</v>
+      </c>
+      <c r="M6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" t="s">
+        <v>63</v>
+      </c>
+      <c r="M7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" t="s">
+        <v>68</v>
+      </c>
+      <c r="M8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" t="s">
+        <v>56</v>
+      </c>
+      <c r="K9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" t="s">
+        <v>74</v>
+      </c>
+      <c r="M9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s">
+        <v>79</v>
+      </c>
+      <c r="I10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" t="s">
+        <v>80</v>
+      </c>
+      <c r="M10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I11" t="s">
+        <v>38</v>
+      </c>
+      <c r="J11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" t="s">
+        <v>86</v>
+      </c>
+      <c r="M11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L12" t="s">
+        <v>91</v>
+      </c>
+      <c r="M12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s">
+        <v>96</v>
+      </c>
+      <c r="I13" t="s">
+        <v>38</v>
+      </c>
+      <c r="J13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" t="s">
+        <v>97</v>
+      </c>
+      <c r="M13" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" t="s">
+        <v>102</v>
+      </c>
+      <c r="J14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" t="s">
+        <v>103</v>
+      </c>
+      <c r="M14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" t="s">
+        <v>56</v>
+      </c>
+      <c r="K15" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" t="s">
+        <v>108</v>
+      </c>
+      <c r="M15" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" t="s">
+        <v>113</v>
+      </c>
+      <c r="J16" t="s">
+        <v>114</v>
+      </c>
+      <c r="K16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L16" t="s">
+        <v>115</v>
+      </c>
+      <c r="M16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" t="s">
+        <v>120</v>
+      </c>
+      <c r="J17" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L17" t="s">
+        <v>121</v>
+      </c>
+      <c r="M17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s">
+        <v>125</v>
+      </c>
+      <c r="E18" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s">
+        <v>46</v>
+      </c>
+      <c r="I18" t="s">
+        <v>38</v>
+      </c>
+      <c r="J18" t="s">
+        <v>126</v>
+      </c>
+      <c r="K18" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18" t="s">
+        <v>127</v>
+      </c>
+      <c r="M18" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" t="s">
+        <v>131</v>
+      </c>
+      <c r="E19" t="s">
+        <v>132</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" t="s">
+        <v>133</v>
+      </c>
+      <c r="M19" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" t="s">
+        <v>137</v>
+      </c>
+      <c r="E20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s">
+        <v>138</v>
+      </c>
+      <c r="I20" t="s">
+        <v>38</v>
+      </c>
+      <c r="J20" t="s">
+        <v>56</v>
+      </c>
+      <c r="K20" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" t="s">
+        <v>139</v>
+      </c>
+      <c r="M20" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>141</v>
+      </c>
+      <c r="B21" t="s">
+        <v>142</v>
+      </c>
+      <c r="C21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" t="s">
+        <v>143</v>
+      </c>
+      <c r="E21" t="s">
+        <v>144</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s">
+        <v>145</v>
+      </c>
+      <c r="I21" t="s">
+        <v>38</v>
+      </c>
+      <c r="J21" t="s">
+        <v>56</v>
+      </c>
+      <c r="K21" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" t="s">
+        <v>146</v>
+      </c>
+      <c r="M21" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" t="s">
+        <v>149</v>
+      </c>
+      <c r="C22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" t="s">
+        <v>150</v>
+      </c>
+      <c r="E22" t="s">
+        <v>151</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s">
+        <v>37</v>
+      </c>
+      <c r="I22" t="s">
+        <v>38</v>
+      </c>
+      <c r="J22" t="s">
+        <v>56</v>
+      </c>
+      <c r="K22" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" t="s">
+        <v>152</v>
+      </c>
+      <c r="M22" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" t="s">
+        <v>155</v>
+      </c>
+      <c r="C23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" t="s">
+        <v>156</v>
+      </c>
+      <c r="E23" t="s">
+        <v>151</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s">
+        <v>37</v>
+      </c>
+      <c r="I23" t="s">
+        <v>38</v>
+      </c>
+      <c r="J23" t="s">
+        <v>56</v>
+      </c>
+      <c r="K23" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" t="s">
+        <v>157</v>
+      </c>
+      <c r="M23" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>159</v>
+      </c>
+      <c r="B24" t="s">
+        <v>160</v>
+      </c>
+      <c r="C24" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" t="s">
+        <v>161</v>
+      </c>
+      <c r="E24" t="s">
+        <v>151</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I24" t="s">
+        <v>38</v>
+      </c>
+      <c r="J24" t="s">
+        <v>20</v>
+      </c>
+      <c r="K24" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" t="s">
+        <v>162</v>
+      </c>
+      <c r="M24" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>164</v>
+      </c>
+      <c r="B25" t="s">
+        <v>165</v>
+      </c>
+      <c r="C25" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" t="s">
+        <v>166</v>
+      </c>
+      <c r="E25" t="s">
+        <v>151</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s">
+        <v>96</v>
+      </c>
+      <c r="I25" t="s">
+        <v>38</v>
+      </c>
+      <c r="J25" t="s">
+        <v>56</v>
+      </c>
+      <c r="K25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" t="s">
+        <v>167</v>
+      </c>
+      <c r="M25" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>169</v>
+      </c>
+      <c r="B26" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" t="s">
+        <v>171</v>
+      </c>
+      <c r="E26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I26" t="s">
+        <v>38</v>
+      </c>
+      <c r="J26" t="s">
+        <v>56</v>
+      </c>
+      <c r="K26" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" t="s">
+        <v>172</v>
+      </c>
+      <c r="M26" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>174</v>
+      </c>
+      <c r="B27" t="s">
+        <v>175</v>
+      </c>
+      <c r="C27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" t="s">
+        <v>176</v>
+      </c>
+      <c r="E27" t="s">
+        <v>151</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I27" t="s">
+        <v>38</v>
+      </c>
+      <c r="J27" t="s">
+        <v>56</v>
+      </c>
+      <c r="K27" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" t="s">
+        <v>177</v>
+      </c>
+      <c r="M27" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>179</v>
+      </c>
+      <c r="B28" t="s">
+        <v>180</v>
+      </c>
+      <c r="C28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" t="s">
+        <v>181</v>
+      </c>
+      <c r="E28" t="s">
+        <v>151</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s">
+        <v>37</v>
+      </c>
+      <c r="I28" t="s">
+        <v>38</v>
+      </c>
+      <c r="J28" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" t="s">
+        <v>182</v>
+      </c>
+      <c r="M28" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>184</v>
+      </c>
+      <c r="B29" t="s">
+        <v>185</v>
+      </c>
+      <c r="C29" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" t="s">
+        <v>186</v>
+      </c>
+      <c r="E29" t="s">
+        <v>151</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s">
+        <v>187</v>
+      </c>
+      <c r="I29" t="s">
+        <v>38</v>
+      </c>
+      <c r="J29" t="s">
+        <v>20</v>
+      </c>
+      <c r="K29" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" t="s">
+        <v>188</v>
+      </c>
+      <c r="M29" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>190</v>
+      </c>
+      <c r="B30" t="s">
+        <v>191</v>
+      </c>
+      <c r="C30" t="s">
+        <v>192</v>
+      </c>
+      <c r="D30" t="s">
+        <v>193</v>
+      </c>
+      <c r="E30" t="s">
+        <v>151</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s">
+        <v>194</v>
+      </c>
+      <c r="I30" t="s">
+        <v>38</v>
+      </c>
+      <c r="J30" t="s">
+        <v>56</v>
+      </c>
+      <c r="K30" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" t="s">
+        <v>195</v>
+      </c>
+      <c r="M30" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>197</v>
+      </c>
+      <c r="B31" t="s">
+        <v>198</v>
+      </c>
+      <c r="C31" t="s">
+        <v>199</v>
+      </c>
+      <c r="D31" t="s">
+        <v>200</v>
+      </c>
+      <c r="E31" t="s">
+        <v>151</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s">
+        <v>20</v>
+      </c>
+      <c r="I31" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" t="s">
+        <v>20</v>
+      </c>
+      <c r="K31" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" t="s">
+        <v>201</v>
+      </c>
+      <c r="M31" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>203</v>
+      </c>
+      <c r="B32" t="s">
+        <v>204</v>
+      </c>
+      <c r="C32" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" t="s">
+        <v>205</v>
+      </c>
+      <c r="E32" t="s">
+        <v>151</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s">
+        <v>206</v>
+      </c>
+      <c r="I32" t="s">
+        <v>38</v>
+      </c>
+      <c r="J32" t="s">
+        <v>20</v>
+      </c>
+      <c r="K32" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" t="s">
+        <v>207</v>
+      </c>
+      <c r="M32" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>209</v>
+      </c>
+      <c r="B33" t="s">
+        <v>210</v>
+      </c>
+      <c r="C33" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" t="s">
+        <v>211</v>
+      </c>
+      <c r="E33" t="s">
+        <v>151</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s">
+        <v>20</v>
+      </c>
+      <c r="I33" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" t="s">
+        <v>212</v>
+      </c>
+      <c r="M33" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>214</v>
+      </c>
+      <c r="B34" t="s">
+        <v>215</v>
+      </c>
+      <c r="C34" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" t="s">
+        <v>216</v>
+      </c>
+      <c r="E34" t="s">
+        <v>151</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s">
+        <v>20</v>
+      </c>
+      <c r="I34" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" t="s">
+        <v>20</v>
+      </c>
+      <c r="K34" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" t="s">
+        <v>217</v>
+      </c>
+      <c r="M34" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>219</v>
+      </c>
+      <c r="B35" t="s">
+        <v>220</v>
+      </c>
+      <c r="C35" t="s">
+        <v>35</v>
+      </c>
+      <c r="D35" t="s">
+        <v>221</v>
+      </c>
+      <c r="E35" t="s">
+        <v>151</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s">
+        <v>37</v>
+      </c>
+      <c r="I35" t="s">
+        <v>38</v>
+      </c>
+      <c r="J35" t="s">
+        <v>56</v>
+      </c>
+      <c r="K35" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" t="s">
+        <v>222</v>
+      </c>
+      <c r="M35" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>224</v>
+      </c>
+      <c r="B36" t="s">
+        <v>225</v>
+      </c>
+      <c r="C36" t="s">
+        <v>226</v>
+      </c>
+      <c r="D36" t="s">
+        <v>227</v>
+      </c>
+      <c r="E36" t="s">
+        <v>151</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s">
+        <v>37</v>
+      </c>
+      <c r="I36" t="s">
+        <v>38</v>
+      </c>
+      <c r="J36" t="s">
+        <v>20</v>
+      </c>
+      <c r="K36" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" t="s">
+        <v>228</v>
+      </c>
+      <c r="M36" t="s">
+        <v>229</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
